--- a/artfynd/A 63702-2025 artfynd.xlsx
+++ b/artfynd/A 63702-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY9"/>
+  <dimension ref="A1:AY23"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -678,12 +678,7 @@
         <v>59966420</v>
       </c>
       <c r="B2" t="n">
-        <v>104643</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>107708</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -726,14 +721,14 @@
       <c r="L2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
-          <t>Stv. Älgsjövägen, Älgsjön, Gstr</t>
+          <t>Stv. Älgsjövägen, Mårtsbo, Gstr</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>623353.2339737939</v>
+        <v>623353</v>
       </c>
       <c r="R2" t="n">
-        <v>6724168.104919133</v>
+        <v>6724168</v>
       </c>
       <c r="S2" t="n">
         <v>50</v>
@@ -763,19 +758,9 @@
           <t>2016-06-03</t>
         </is>
       </c>
-      <c r="Z2" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA2" t="inlineStr">
         <is>
           <t>2016-06-03</t>
-        </is>
-      </c>
-      <c r="AB2" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AC2" t="inlineStr">
@@ -807,53 +792,64 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>68512106</v>
+        <v>73366562</v>
       </c>
       <c r="B3" t="n">
-        <v>99398</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>107708</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>221235</v>
+        <v>245</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Vårärt</t>
+          <t>Skogsklocka</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Lathyrus vernus</t>
+          <t>Campanula cervicaria</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(L.) Bernh.</t>
-        </is>
-      </c>
-      <c r="I3" t="inlineStr"/>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>80</t>
+        </is>
+      </c>
+      <c r="J3" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K3" t="inlineStr">
+        <is>
+          <t>överblommad</t>
+        </is>
+      </c>
+      <c r="L3" t="inlineStr"/>
+      <c r="N3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
-          <t>Öster Älgsjön, Gstr</t>
+          <t>Långbro, sydostom Stortärnan , Gstr</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>623256.8415235602</v>
+        <v>623343</v>
       </c>
       <c r="R3" t="n">
-        <v>6723995.882547948</v>
+        <v>6724216</v>
       </c>
       <c r="S3" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -877,22 +873,17 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>2017-08-31</t>
-        </is>
-      </c>
-      <c r="Z3" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2018-09-22</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>2017-08-31</t>
-        </is>
-      </c>
-      <c r="AB3" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2018-09-22</t>
+        </is>
+      </c>
+      <c r="AC3" t="inlineStr">
+        <is>
+          <t>kring gammal grustäkt</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -901,60 +892,56 @@
       <c r="AE3" t="b">
         <v>0</v>
       </c>
+      <c r="AF3" t="inlineStr"/>
       <c r="AG3" t="b">
         <v>0</v>
       </c>
       <c r="AI3" t="inlineStr">
         <is>
-          <t>olikåldrig gammal blandsumpskog</t>
+          <t>skogsväg och vägficka</t>
         </is>
       </c>
       <c r="AT3" t="inlineStr"/>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>Magnus Andersson</t>
+          <t>Peter Ståhl</t>
         </is>
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>Magnus Andersson</t>
+          <t>Peter Ståhl, Inga-Greta Andersson</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>73366614</v>
+        <v>74250550</v>
       </c>
       <c r="B4" t="n">
-        <v>103252</v>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>107708</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>224098</v>
+        <v>245</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Kalktallört</t>
+          <t>Skogsklocka</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Monotropa hypophegea</t>
+          <t>Campanula cervicaria</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>Wallr.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
@@ -968,21 +955,20 @@
         </is>
       </c>
       <c r="K4" t="inlineStr"/>
-      <c r="L4" t="inlineStr"/>
       <c r="N4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
-          <t>Älgsjömuren norr om, Gstr</t>
+          <t>Älgsjömuren NNO, vid skarp vägkurva, Gstr</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>623254.0399041541</v>
+        <v>623364</v>
       </c>
       <c r="R4" t="n">
-        <v>6724106.269899268</v>
+        <v>6724221</v>
       </c>
       <c r="S4" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
@@ -1004,24 +990,24 @@
           <t>Gävle</t>
         </is>
       </c>
+      <c r="X4" t="inlineStr">
+        <is>
+          <t>XG-Gäv-0573</t>
+        </is>
+      </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>2018-09-22</t>
-        </is>
-      </c>
-      <c r="Z4" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2007-07-14</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>2018-09-22</t>
-        </is>
-      </c>
-      <c r="AB4" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2007-07-14</t>
+        </is>
+      </c>
+      <c r="AC4" t="inlineStr">
+        <is>
+          <t>1 ex med mest vissna blommor, nyfynd</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1036,7 +1022,7 @@
       </c>
       <c r="AI4" t="inlineStr">
         <is>
-          <t>kalkrik barrskog</t>
+          <t>Kulturmark, grustag utmed skogsväg bland uppkastade block</t>
         </is>
       </c>
       <c r="AT4" t="inlineStr"/>
@@ -1047,39 +1033,38 @@
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>Peter Ståhl, Inga-Greta Andersson</t>
-        </is>
-      </c>
-      <c r="AY4" t="inlineStr"/>
+          <t>Birgitta Hellström</t>
+        </is>
+      </c>
+      <c r="AY4" t="inlineStr">
+        <is>
+          <t>Floraväkteri Sverige</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>73366562</v>
+        <v>91244189</v>
       </c>
       <c r="B5" t="n">
-        <v>104643</v>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99024</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>245</v>
+        <v>504</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Skogsklocka</t>
+          <t>Guckusko</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Campanula cervicaria</t>
+          <t>Cypripedium calceolus</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
@@ -1087,36 +1072,20 @@
           <t>L.</t>
         </is>
       </c>
-      <c r="I5" t="inlineStr">
-        <is>
-          <t>80</t>
-        </is>
-      </c>
-      <c r="J5" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K5" t="inlineStr">
-        <is>
-          <t>överblommad</t>
-        </is>
-      </c>
-      <c r="L5" t="inlineStr"/>
-      <c r="N5" t="inlineStr"/>
+      <c r="I5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
-          <t>Långbro, sydostom Stortärnan , Gstr</t>
+          <t>Älgsjön 1 km NO, Gstr</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>623342.7254283859</v>
+        <v>623249</v>
       </c>
       <c r="R5" t="n">
-        <v>6724216.355189564</v>
+        <v>6724011</v>
       </c>
       <c r="S5" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
@@ -1140,27 +1109,12 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>2018-09-22</t>
-        </is>
-      </c>
-      <c r="Z5" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2012-08-08</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
         <is>
-          <t>2018-09-22</t>
-        </is>
-      </c>
-      <c r="AB5" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
-      <c r="AC5" t="inlineStr">
-        <is>
-          <t>kring gammal grustäkt</t>
+          <t>2012-08-08</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1169,13 +1123,17 @@
       <c r="AE5" t="b">
         <v>0</v>
       </c>
-      <c r="AF5" t="inlineStr"/>
       <c r="AG5" t="b">
         <v>0</v>
       </c>
       <c r="AI5" t="inlineStr">
         <is>
-          <t>skogsväg och vägficka</t>
+          <t>Sumpskog, kalkrik lövinblandad, fina mossytor och örtrikt</t>
+        </is>
+      </c>
+      <c r="AR5" t="inlineStr">
+        <is>
+          <t>Gst Fyndnr 312757N</t>
         </is>
       </c>
       <c r="AT5" t="inlineStr"/>
@@ -1186,22 +1144,21 @@
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>Peter Ståhl, Inga-Greta Andersson</t>
-        </is>
-      </c>
-      <c r="AY5" t="inlineStr"/>
+          <t>Peter Ståhl</t>
+        </is>
+      </c>
+      <c r="AY5" t="inlineStr">
+        <is>
+          <t>Gästriklands flora (2016)</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>73366585</v>
+        <v>96852574</v>
       </c>
       <c r="B6" t="n">
-        <v>85077</v>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99024</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1209,39 +1166,49 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>3762</v>
+        <v>504</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Olivspindling</t>
+          <t>Guckusko</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Cortinarius venetus</t>
+          <t>Cypripedium calceolus</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) Fr.</t>
-        </is>
-      </c>
-      <c r="I6" t="inlineStr"/>
-      <c r="J6" t="inlineStr"/>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>13</t>
+        </is>
+      </c>
+      <c r="J6" t="inlineStr">
+        <is>
+          <t>stjälkar/strån/skott</t>
+        </is>
+      </c>
       <c r="K6" t="inlineStr"/>
+      <c r="L6" t="inlineStr"/>
+      <c r="N6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
-          <t>Långbro, sydost Stortärnan, Gstr</t>
+          <t>Gävle, Gstr</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>623321.7538489607</v>
+        <v>623176</v>
       </c>
       <c r="R6" t="n">
-        <v>6724211.216418002</v>
+        <v>6724176</v>
       </c>
       <c r="S6" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
@@ -1265,22 +1232,27 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>2018-09-22</t>
+          <t>2021-10-26</t>
         </is>
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>00:00</t>
+          <t>16:02</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
         <is>
-          <t>2018-09-22</t>
+          <t>2021-10-26</t>
         </is>
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>00:00</t>
+          <t>16:02</t>
+        </is>
+      </c>
+      <c r="AC6" t="inlineStr">
+        <is>
+          <t>3 skott där en bär frukt samt ytterligare en lite större grupp kanske 10 m längre bort där 5-6 stänglar satt frukt! Allt svart så här års.</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1301,61 +1273,64 @@
       </c>
       <c r="AX6" t="inlineStr">
         <is>
-          <t>Peter Ståhl, Inga-Greta Andersson</t>
+          <t>Peter Ståhl</t>
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>73366627</v>
+        <v>127802330</v>
       </c>
       <c r="B7" t="n">
-        <v>100515</v>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99024</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>CR</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>223246</v>
+        <v>504</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Skogsalm</t>
+          <t>Guckusko</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Ulmus glabra</t>
+          <t>Cypripedium calceolus</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>Huds.</t>
-        </is>
-      </c>
-      <c r="I7" t="inlineStr"/>
-      <c r="J7" t="inlineStr"/>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>60</t>
+        </is>
+      </c>
+      <c r="J7" t="inlineStr">
+        <is>
+          <t>stjälkar/strån/skott</t>
+        </is>
+      </c>
       <c r="K7" t="inlineStr"/>
       <c r="L7" t="inlineStr"/>
       <c r="N7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
-          <t>Älgsjömuren norr om, Gstr</t>
+          <t>Gävle, Gävle, Gstr</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>623238.5890221413</v>
+        <v>623175</v>
       </c>
       <c r="R7" t="n">
-        <v>6724097.883616832</v>
+        <v>6724187</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1382,27 +1357,27 @@
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>2018-09-22</t>
+          <t>2025-08-25</t>
         </is>
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>00:00</t>
+          <t>15:18</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
         <is>
-          <t>2018-09-22</t>
+          <t>2025-08-25</t>
         </is>
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>00:00</t>
+          <t>15:18</t>
         </is>
       </c>
       <c r="AC7" t="inlineStr">
         <is>
-          <t>buskformiga</t>
+          <t>En klunga med 11 blomstänglar samt ytterligare två bestånd ca 10m bort</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1415,11 +1390,6 @@
       <c r="AG7" t="b">
         <v>0</v>
       </c>
-      <c r="AI7" t="inlineStr">
-        <is>
-          <t>kalkrik barrskog</t>
-        </is>
-      </c>
       <c r="AT7" t="inlineStr"/>
       <c r="AW7" t="inlineStr">
         <is>
@@ -1428,52 +1398,52 @@
       </c>
       <c r="AX7" t="inlineStr">
         <is>
-          <t>Peter Ståhl, Inga-Greta Andersson</t>
+          <t>Peter Ståhl</t>
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>93811407</v>
+        <v>431483</v>
       </c>
       <c r="B8" t="n">
-        <v>98637</v>
+        <v>97776</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>219798</v>
+        <v>1590</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Skogsknipprot</t>
+          <t>Dunmossa</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Epipactis helleborine</t>
+          <t>Trichocolea tomentella</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(L.) Crantz</t>
+          <t>(Ehrh.) Dumort.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
-          <t>Älgsjön 1 km NO, O om Älgsjövägen, Gstr</t>
+          <t>Älgsjön NO, 650-750 m NO kanalens utlopp ur Älgsjön., Gstr</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>623260</v>
+        <v>623204</v>
       </c>
       <c r="R8" t="n">
-        <v>6724252</v>
+        <v>6724063</v>
       </c>
       <c r="S8" t="n">
         <v>25</v>
@@ -1500,12 +1470,17 @@
       </c>
       <c r="Y8" t="inlineStr">
         <is>
-          <t>2005-07-29</t>
+          <t>1999-09-18</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
         <is>
-          <t>2005-07-29</t>
+          <t>1999-09-18</t>
+        </is>
+      </c>
+      <c r="AC8" t="inlineStr">
+        <is>
+          <t>Riklig inom flera koordinat. Nyfynd</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1519,12 +1494,7 @@
       </c>
       <c r="AI8" t="inlineStr">
         <is>
-          <t>Kulturmark, vägkant vid skogsbilväg</t>
-        </is>
-      </c>
-      <c r="AR8" t="inlineStr">
-        <is>
-          <t>Gst Fyndnr 280164H</t>
+          <t>Sumpskog, blandskog, sluten fuktig,  kalkhaltig mark</t>
         </is>
       </c>
       <c r="AT8" t="inlineStr"/>
@@ -1535,26 +1505,17 @@
       </c>
       <c r="AX8" t="inlineStr">
         <is>
-          <t>Birgitta Hellström</t>
-        </is>
-      </c>
-      <c r="AY8" t="inlineStr">
-        <is>
-          <t>Gästriklands flora (2016)</t>
-        </is>
-      </c>
+          <t>Peter Ståhl, Birgitta Hellström</t>
+        </is>
+      </c>
+      <c r="AY8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>110157792</v>
+        <v>436422</v>
       </c>
       <c r="B9" t="n">
-        <v>106707</v>
-      </c>
-      <c r="C9" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>97776</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1562,35 +1523,34 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>220204</v>
+        <v>1590</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Slåtterfibbla</t>
+          <t>Dunmossa</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Hypochaeris maculata</t>
+          <t>Trichocolea tomentella</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Ehrh.) Dumort.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
-      <c r="K9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
-          <t>Stortärnan, Gstr</t>
+          <t>Älgsjön 1 km NO, Gstr</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>623328.7536306498</v>
+        <v>623259</v>
       </c>
       <c r="R9" t="n">
-        <v>6724078.879726081</v>
+        <v>6724046</v>
       </c>
       <c r="S9" t="n">
         <v>25</v>
@@ -1617,22 +1577,17 @@
       </c>
       <c r="Y9" t="inlineStr">
         <is>
-          <t>2023-06-17</t>
-        </is>
-      </c>
-      <c r="Z9" t="inlineStr">
-        <is>
-          <t>15:16</t>
+          <t>2012-08-08</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
         <is>
-          <t>2023-06-17</t>
-        </is>
-      </c>
-      <c r="AB9" t="inlineStr">
-        <is>
-          <t>15:16</t>
+          <t>2012-08-08</t>
+        </is>
+      </c>
+      <c r="AC9" t="inlineStr">
+        <is>
+          <t>MASSOR! Längs flera 100 m långt stråk</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1643,19 +1598,1525 @@
       </c>
       <c r="AG9" t="b">
         <v>0</v>
+      </c>
+      <c r="AI9" t="inlineStr">
+        <is>
+          <t>Sumpskog, barrdominerad med löv, stark kalkpåverkan</t>
+        </is>
       </c>
       <c r="AT9" t="inlineStr"/>
       <c r="AW9" t="inlineStr">
         <is>
+          <t>Peter Ståhl</t>
+        </is>
+      </c>
+      <c r="AX9" t="inlineStr">
+        <is>
+          <t>Peter Ståhl</t>
+        </is>
+      </c>
+      <c r="AY9" t="inlineStr"/>
+    </row>
+    <row r="10">
+      <c r="A10" t="n">
+        <v>436423</v>
+      </c>
+      <c r="B10" t="n">
+        <v>97776</v>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E10" t="n">
+        <v>1590</v>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>Dunmossa</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>Trichocolea tomentella</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>(Ehrh.) Dumort.</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr"/>
+      <c r="P10" t="inlineStr">
+        <is>
+          <t>Älgsjön 1 km NO, Gstr</t>
+        </is>
+      </c>
+      <c r="Q10" t="n">
+        <v>623249</v>
+      </c>
+      <c r="R10" t="n">
+        <v>6724011</v>
+      </c>
+      <c r="S10" t="n">
+        <v>25</v>
+      </c>
+      <c r="T10" t="inlineStr">
+        <is>
+          <t>Gävleborg</t>
+        </is>
+      </c>
+      <c r="U10" t="inlineStr">
+        <is>
+          <t>Gävle</t>
+        </is>
+      </c>
+      <c r="V10" t="inlineStr">
+        <is>
+          <t>Gästrikland</t>
+        </is>
+      </c>
+      <c r="W10" t="inlineStr">
+        <is>
+          <t>Gävle</t>
+        </is>
+      </c>
+      <c r="Y10" t="inlineStr">
+        <is>
+          <t>2012-08-08</t>
+        </is>
+      </c>
+      <c r="AA10" t="inlineStr">
+        <is>
+          <t>2012-08-08</t>
+        </is>
+      </c>
+      <c r="AC10" t="inlineStr">
+        <is>
+          <t>MASSOR! Längs flera 100 m långt stråk</t>
+        </is>
+      </c>
+      <c r="AD10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI10" t="inlineStr">
+        <is>
+          <t>Sumpskog, kalkrik lövinblandad, fina mossmattor</t>
+        </is>
+      </c>
+      <c r="AT10" t="inlineStr"/>
+      <c r="AW10" t="inlineStr">
+        <is>
+          <t>Peter Ståhl</t>
+        </is>
+      </c>
+      <c r="AX10" t="inlineStr">
+        <is>
+          <t>Peter Ståhl</t>
+        </is>
+      </c>
+      <c r="AY10" t="inlineStr"/>
+    </row>
+    <row r="11">
+      <c r="A11" t="n">
+        <v>436685</v>
+      </c>
+      <c r="B11" t="n">
+        <v>97776</v>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E11" t="n">
+        <v>1590</v>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>Dunmossa</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>Trichocolea tomentella</t>
+        </is>
+      </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>(Ehrh.) Dumort.</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr"/>
+      <c r="P11" t="inlineStr">
+        <is>
+          <t>Norr om Älgsjömuren, Gstr</t>
+        </is>
+      </c>
+      <c r="Q11" t="n">
+        <v>623232</v>
+      </c>
+      <c r="R11" t="n">
+        <v>6724021</v>
+      </c>
+      <c r="S11" t="n">
+        <v>10</v>
+      </c>
+      <c r="T11" t="inlineStr">
+        <is>
+          <t>Gävleborg</t>
+        </is>
+      </c>
+      <c r="U11" t="inlineStr">
+        <is>
+          <t>Gävle</t>
+        </is>
+      </c>
+      <c r="V11" t="inlineStr">
+        <is>
+          <t>Gästrikland</t>
+        </is>
+      </c>
+      <c r="W11" t="inlineStr">
+        <is>
+          <t>Gävle</t>
+        </is>
+      </c>
+      <c r="Y11" t="inlineStr">
+        <is>
+          <t>2013-05-11</t>
+        </is>
+      </c>
+      <c r="AA11" t="inlineStr">
+        <is>
+          <t>2013-05-11</t>
+        </is>
+      </c>
+      <c r="AD11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI11" t="inlineStr">
+        <is>
+          <t>blandsumpskog</t>
+        </is>
+      </c>
+      <c r="AT11" t="inlineStr"/>
+      <c r="AW11" t="inlineStr">
+        <is>
+          <t>Tomas Troschke</t>
+        </is>
+      </c>
+      <c r="AX11" t="inlineStr">
+        <is>
+          <t>Via Tomas Troschke</t>
+        </is>
+      </c>
+      <c r="AY11" t="inlineStr"/>
+    </row>
+    <row r="12">
+      <c r="A12" t="n">
+        <v>68512105</v>
+      </c>
+      <c r="B12" t="n">
+        <v>97776</v>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E12" t="n">
+        <v>1590</v>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>Dunmossa</t>
+        </is>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>Trichocolea tomentella</t>
+        </is>
+      </c>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>(Ehrh.) Dumort.</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J12" t="inlineStr">
+        <is>
+          <t>m²</t>
+        </is>
+      </c>
+      <c r="P12" t="inlineStr">
+        <is>
+          <t>Öster Älgsjön, Gstr</t>
+        </is>
+      </c>
+      <c r="Q12" t="n">
+        <v>623245</v>
+      </c>
+      <c r="R12" t="n">
+        <v>6724008</v>
+      </c>
+      <c r="S12" t="n">
+        <v>25</v>
+      </c>
+      <c r="T12" t="inlineStr">
+        <is>
+          <t>Gävleborg</t>
+        </is>
+      </c>
+      <c r="U12" t="inlineStr">
+        <is>
+          <t>Gävle</t>
+        </is>
+      </c>
+      <c r="V12" t="inlineStr">
+        <is>
+          <t>Gästrikland</t>
+        </is>
+      </c>
+      <c r="W12" t="inlineStr">
+        <is>
+          <t>Gävle</t>
+        </is>
+      </c>
+      <c r="Y12" t="inlineStr">
+        <is>
+          <t>2017-08-31</t>
+        </is>
+      </c>
+      <c r="AA12" t="inlineStr">
+        <is>
+          <t>2017-08-31</t>
+        </is>
+      </c>
+      <c r="AD12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI12" t="inlineStr">
+        <is>
+          <t>olikåldrig gammal blandsumpskog</t>
+        </is>
+      </c>
+      <c r="AT12" t="inlineStr"/>
+      <c r="AW12" t="inlineStr">
+        <is>
+          <t>Magnus Andersson</t>
+        </is>
+      </c>
+      <c r="AX12" t="inlineStr">
+        <is>
+          <t>Magnus Andersson</t>
+        </is>
+      </c>
+      <c r="AY12" t="inlineStr"/>
+    </row>
+    <row r="13">
+      <c r="A13" t="n">
+        <v>96852676</v>
+      </c>
+      <c r="B13" t="n">
+        <v>97231</v>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E13" t="n">
+        <v>2869</v>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>Bollvitmossa</t>
+        </is>
+      </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>Sphagnum wulfianum</t>
+        </is>
+      </c>
+      <c r="H13" t="inlineStr">
+        <is>
+          <t>Girg.</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr"/>
+      <c r="K13" t="inlineStr"/>
+      <c r="L13" t="inlineStr"/>
+      <c r="P13" t="inlineStr">
+        <is>
+          <t>Gävle, Gstr</t>
+        </is>
+      </c>
+      <c r="Q13" t="n">
+        <v>623172</v>
+      </c>
+      <c r="R13" t="n">
+        <v>6724178</v>
+      </c>
+      <c r="S13" t="n">
+        <v>25</v>
+      </c>
+      <c r="T13" t="inlineStr">
+        <is>
+          <t>Gävleborg</t>
+        </is>
+      </c>
+      <c r="U13" t="inlineStr">
+        <is>
+          <t>Gävle</t>
+        </is>
+      </c>
+      <c r="V13" t="inlineStr">
+        <is>
+          <t>Gästrikland</t>
+        </is>
+      </c>
+      <c r="W13" t="inlineStr">
+        <is>
+          <t>Gävle</t>
+        </is>
+      </c>
+      <c r="Y13" t="inlineStr">
+        <is>
+          <t>2021-10-26</t>
+        </is>
+      </c>
+      <c r="Z13" t="inlineStr">
+        <is>
+          <t>16:13</t>
+        </is>
+      </c>
+      <c r="AA13" t="inlineStr">
+        <is>
+          <t>2021-10-26</t>
+        </is>
+      </c>
+      <c r="AB13" t="inlineStr">
+        <is>
+          <t>16:13</t>
+        </is>
+      </c>
+      <c r="AD13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT13" t="inlineStr"/>
+      <c r="AW13" t="inlineStr">
+        <is>
+          <t>Peter Ståhl</t>
+        </is>
+      </c>
+      <c r="AX13" t="inlineStr">
+        <is>
+          <t>Peter Ståhl</t>
+        </is>
+      </c>
+      <c r="AY13" t="inlineStr"/>
+    </row>
+    <row r="14">
+      <c r="A14" t="n">
+        <v>73366585</v>
+      </c>
+      <c r="B14" t="n">
+        <v>87146</v>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E14" t="n">
+        <v>3762</v>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>Olivspindling</t>
+        </is>
+      </c>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>Cortinarius venetus</t>
+        </is>
+      </c>
+      <c r="H14" t="inlineStr">
+        <is>
+          <t>(Fr.:Fr.) Fr.</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr"/>
+      <c r="J14" t="inlineStr"/>
+      <c r="K14" t="inlineStr"/>
+      <c r="P14" t="inlineStr">
+        <is>
+          <t>Långbro, sydost Stortärnan, Gstr</t>
+        </is>
+      </c>
+      <c r="Q14" t="n">
+        <v>623322</v>
+      </c>
+      <c r="R14" t="n">
+        <v>6724211</v>
+      </c>
+      <c r="S14" t="n">
+        <v>10</v>
+      </c>
+      <c r="T14" t="inlineStr">
+        <is>
+          <t>Gävleborg</t>
+        </is>
+      </c>
+      <c r="U14" t="inlineStr">
+        <is>
+          <t>Gävle</t>
+        </is>
+      </c>
+      <c r="V14" t="inlineStr">
+        <is>
+          <t>Gästrikland</t>
+        </is>
+      </c>
+      <c r="W14" t="inlineStr">
+        <is>
+          <t>Gävle</t>
+        </is>
+      </c>
+      <c r="Y14" t="inlineStr">
+        <is>
+          <t>2018-09-22</t>
+        </is>
+      </c>
+      <c r="AA14" t="inlineStr">
+        <is>
+          <t>2018-09-22</t>
+        </is>
+      </c>
+      <c r="AD14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF14" t="inlineStr"/>
+      <c r="AG14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT14" t="inlineStr"/>
+      <c r="AW14" t="inlineStr">
+        <is>
+          <t>Peter Ståhl</t>
+        </is>
+      </c>
+      <c r="AX14" t="inlineStr">
+        <is>
+          <t>Peter Ståhl, Inga-Greta Andersson</t>
+        </is>
+      </c>
+      <c r="AY14" t="inlineStr"/>
+    </row>
+    <row r="15">
+      <c r="A15" t="n">
+        <v>93811407</v>
+      </c>
+      <c r="B15" t="n">
+        <v>99096</v>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E15" t="n">
+        <v>219798</v>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>Skogsknipprot</t>
+        </is>
+      </c>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>Epipactis helleborine</t>
+        </is>
+      </c>
+      <c r="H15" t="inlineStr">
+        <is>
+          <t>(L.) Crantz</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr"/>
+      <c r="P15" t="inlineStr">
+        <is>
+          <t>Älgsjön 1 km NO, O om Älgsjövägen, Gstr</t>
+        </is>
+      </c>
+      <c r="Q15" t="n">
+        <v>623260</v>
+      </c>
+      <c r="R15" t="n">
+        <v>6724252</v>
+      </c>
+      <c r="S15" t="n">
+        <v>25</v>
+      </c>
+      <c r="T15" t="inlineStr">
+        <is>
+          <t>Gävleborg</t>
+        </is>
+      </c>
+      <c r="U15" t="inlineStr">
+        <is>
+          <t>Gävle</t>
+        </is>
+      </c>
+      <c r="V15" t="inlineStr">
+        <is>
+          <t>Gästrikland</t>
+        </is>
+      </c>
+      <c r="W15" t="inlineStr">
+        <is>
+          <t>Gävle</t>
+        </is>
+      </c>
+      <c r="Y15" t="inlineStr">
+        <is>
+          <t>2005-07-29</t>
+        </is>
+      </c>
+      <c r="AA15" t="inlineStr">
+        <is>
+          <t>2005-07-29</t>
+        </is>
+      </c>
+      <c r="AD15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI15" t="inlineStr">
+        <is>
+          <t>Kulturmark, vägkant vid skogsbilväg</t>
+        </is>
+      </c>
+      <c r="AR15" t="inlineStr">
+        <is>
+          <t>Gst Fyndnr 280164H</t>
+        </is>
+      </c>
+      <c r="AT15" t="inlineStr"/>
+      <c r="AW15" t="inlineStr">
+        <is>
+          <t>Peter Ståhl</t>
+        </is>
+      </c>
+      <c r="AX15" t="inlineStr">
+        <is>
+          <t>Birgitta Hellström</t>
+        </is>
+      </c>
+      <c r="AY15" t="inlineStr">
+        <is>
+          <t>Gästriklands flora (2016)</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="n">
+        <v>68512104</v>
+      </c>
+      <c r="B16" t="n">
+        <v>99142</v>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E16" t="n">
+        <v>219847</v>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>Tvåblad</t>
+        </is>
+      </c>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>Neottia ovata</t>
+        </is>
+      </c>
+      <c r="H16" t="inlineStr">
+        <is>
+          <t>(L.) Buff. &amp; Fingerh.</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr"/>
+      <c r="P16" t="inlineStr">
+        <is>
+          <t>Öster Älgsjön, Gstr</t>
+        </is>
+      </c>
+      <c r="Q16" t="n">
+        <v>623243</v>
+      </c>
+      <c r="R16" t="n">
+        <v>6723992</v>
+      </c>
+      <c r="S16" t="n">
+        <v>25</v>
+      </c>
+      <c r="T16" t="inlineStr">
+        <is>
+          <t>Gävleborg</t>
+        </is>
+      </c>
+      <c r="U16" t="inlineStr">
+        <is>
+          <t>Gävle</t>
+        </is>
+      </c>
+      <c r="V16" t="inlineStr">
+        <is>
+          <t>Gästrikland</t>
+        </is>
+      </c>
+      <c r="W16" t="inlineStr">
+        <is>
+          <t>Gävle</t>
+        </is>
+      </c>
+      <c r="Y16" t="inlineStr">
+        <is>
+          <t>2017-08-31</t>
+        </is>
+      </c>
+      <c r="AA16" t="inlineStr">
+        <is>
+          <t>2017-08-31</t>
+        </is>
+      </c>
+      <c r="AD16" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE16" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG16" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI16" t="inlineStr">
+        <is>
+          <t>olikåldrig gammal blandsumpskog</t>
+        </is>
+      </c>
+      <c r="AT16" t="inlineStr"/>
+      <c r="AW16" t="inlineStr">
+        <is>
+          <t>Magnus Andersson</t>
+        </is>
+      </c>
+      <c r="AX16" t="inlineStr">
+        <is>
+          <t>Magnus Andersson</t>
+        </is>
+      </c>
+      <c r="AY16" t="inlineStr"/>
+    </row>
+    <row r="17">
+      <c r="A17" t="n">
+        <v>110157792</v>
+      </c>
+      <c r="B17" t="n">
+        <v>109815</v>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E17" t="n">
+        <v>220204</v>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>Slåtterfibbla</t>
+        </is>
+      </c>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>Hypochaeris maculata</t>
+        </is>
+      </c>
+      <c r="H17" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr"/>
+      <c r="K17" t="inlineStr"/>
+      <c r="P17" t="inlineStr">
+        <is>
+          <t>Stortärnan, Gstr</t>
+        </is>
+      </c>
+      <c r="Q17" t="n">
+        <v>623329</v>
+      </c>
+      <c r="R17" t="n">
+        <v>6724079</v>
+      </c>
+      <c r="S17" t="n">
+        <v>25</v>
+      </c>
+      <c r="T17" t="inlineStr">
+        <is>
+          <t>Gävleborg</t>
+        </is>
+      </c>
+      <c r="U17" t="inlineStr">
+        <is>
+          <t>Gävle</t>
+        </is>
+      </c>
+      <c r="V17" t="inlineStr">
+        <is>
+          <t>Gästrikland</t>
+        </is>
+      </c>
+      <c r="W17" t="inlineStr">
+        <is>
+          <t>Gävle</t>
+        </is>
+      </c>
+      <c r="Y17" t="inlineStr">
+        <is>
+          <t>2023-06-17</t>
+        </is>
+      </c>
+      <c r="Z17" t="inlineStr">
+        <is>
+          <t>15:16</t>
+        </is>
+      </c>
+      <c r="AA17" t="inlineStr">
+        <is>
+          <t>2023-06-17</t>
+        </is>
+      </c>
+      <c r="AB17" t="inlineStr">
+        <is>
+          <t>15:16</t>
+        </is>
+      </c>
+      <c r="AD17" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE17" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG17" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT17" t="inlineStr"/>
+      <c r="AW17" t="inlineStr">
+        <is>
           <t>Magnus Stenmark</t>
         </is>
       </c>
-      <c r="AX9" t="inlineStr">
+      <c r="AX17" t="inlineStr">
         <is>
           <t>Magnus Stenmark</t>
         </is>
       </c>
-      <c r="AY9" t="inlineStr"/>
+      <c r="AY17" t="inlineStr"/>
+    </row>
+    <row r="18">
+      <c r="A18" t="n">
+        <v>96853012</v>
+      </c>
+      <c r="B18" t="n">
+        <v>99118</v>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E18" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G18" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H18" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr"/>
+      <c r="K18" t="inlineStr"/>
+      <c r="L18" t="inlineStr"/>
+      <c r="P18" t="inlineStr">
+        <is>
+          <t>Gävle, Gstr</t>
+        </is>
+      </c>
+      <c r="Q18" t="n">
+        <v>623160</v>
+      </c>
+      <c r="R18" t="n">
+        <v>6724090</v>
+      </c>
+      <c r="S18" t="n">
+        <v>25</v>
+      </c>
+      <c r="T18" t="inlineStr">
+        <is>
+          <t>Gävleborg</t>
+        </is>
+      </c>
+      <c r="U18" t="inlineStr">
+        <is>
+          <t>Gävle</t>
+        </is>
+      </c>
+      <c r="V18" t="inlineStr">
+        <is>
+          <t>Gästrikland</t>
+        </is>
+      </c>
+      <c r="W18" t="inlineStr">
+        <is>
+          <t>Gävle</t>
+        </is>
+      </c>
+      <c r="Y18" t="inlineStr">
+        <is>
+          <t>2021-10-26</t>
+        </is>
+      </c>
+      <c r="Z18" t="inlineStr">
+        <is>
+          <t>16:13</t>
+        </is>
+      </c>
+      <c r="AA18" t="inlineStr">
+        <is>
+          <t>2021-10-26</t>
+        </is>
+      </c>
+      <c r="AB18" t="inlineStr">
+        <is>
+          <t>16:13</t>
+        </is>
+      </c>
+      <c r="AD18" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE18" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG18" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT18" t="inlineStr"/>
+      <c r="AW18" t="inlineStr">
+        <is>
+          <t>Peter Ståhl</t>
+        </is>
+      </c>
+      <c r="AX18" t="inlineStr">
+        <is>
+          <t>Peter Ståhl</t>
+        </is>
+      </c>
+      <c r="AY18" t="inlineStr"/>
+    </row>
+    <row r="19">
+      <c r="A19" t="n">
+        <v>91244192</v>
+      </c>
+      <c r="B19" t="n">
+        <v>98030</v>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E19" t="n">
+        <v>221063</v>
+      </c>
+      <c r="F19" t="inlineStr">
+        <is>
+          <t>Trådfräken</t>
+        </is>
+      </c>
+      <c r="G19" t="inlineStr">
+        <is>
+          <t>Equisetum scirpoides</t>
+        </is>
+      </c>
+      <c r="H19" t="inlineStr">
+        <is>
+          <t>Michx.</t>
+        </is>
+      </c>
+      <c r="I19" t="inlineStr"/>
+      <c r="P19" t="inlineStr">
+        <is>
+          <t>Älgsjön 1 km NO, Gstr</t>
+        </is>
+      </c>
+      <c r="Q19" t="n">
+        <v>623259</v>
+      </c>
+      <c r="R19" t="n">
+        <v>6724046</v>
+      </c>
+      <c r="S19" t="n">
+        <v>25</v>
+      </c>
+      <c r="T19" t="inlineStr">
+        <is>
+          <t>Gävleborg</t>
+        </is>
+      </c>
+      <c r="U19" t="inlineStr">
+        <is>
+          <t>Gävle</t>
+        </is>
+      </c>
+      <c r="V19" t="inlineStr">
+        <is>
+          <t>Gästrikland</t>
+        </is>
+      </c>
+      <c r="W19" t="inlineStr">
+        <is>
+          <t>Gävle</t>
+        </is>
+      </c>
+      <c r="Y19" t="inlineStr">
+        <is>
+          <t>2012-08-08</t>
+        </is>
+      </c>
+      <c r="AA19" t="inlineStr">
+        <is>
+          <t>2012-08-08</t>
+        </is>
+      </c>
+      <c r="AD19" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE19" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG19" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI19" t="inlineStr">
+        <is>
+          <t>Sumpskog, barrdominerad med löv, stark kalkpåverkan</t>
+        </is>
+      </c>
+      <c r="AR19" t="inlineStr">
+        <is>
+          <t>Gst Fyndnr 312754N</t>
+        </is>
+      </c>
+      <c r="AT19" t="inlineStr"/>
+      <c r="AW19" t="inlineStr">
+        <is>
+          <t>Peter Ståhl</t>
+        </is>
+      </c>
+      <c r="AX19" t="inlineStr">
+        <is>
+          <t>Peter Ståhl</t>
+        </is>
+      </c>
+      <c r="AY19" t="inlineStr">
+        <is>
+          <t>Gästriklands flora (2016)</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="n">
+        <v>68512106</v>
+      </c>
+      <c r="B20" t="n">
+        <v>102241</v>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E20" t="n">
+        <v>221235</v>
+      </c>
+      <c r="F20" t="inlineStr">
+        <is>
+          <t>Vårärt</t>
+        </is>
+      </c>
+      <c r="G20" t="inlineStr">
+        <is>
+          <t>Lathyrus vernus</t>
+        </is>
+      </c>
+      <c r="H20" t="inlineStr">
+        <is>
+          <t>(L.) Bernh.</t>
+        </is>
+      </c>
+      <c r="I20" t="inlineStr"/>
+      <c r="P20" t="inlineStr">
+        <is>
+          <t>Öster Älgsjön, Gstr</t>
+        </is>
+      </c>
+      <c r="Q20" t="n">
+        <v>623257</v>
+      </c>
+      <c r="R20" t="n">
+        <v>6723996</v>
+      </c>
+      <c r="S20" t="n">
+        <v>25</v>
+      </c>
+      <c r="T20" t="inlineStr">
+        <is>
+          <t>Gävleborg</t>
+        </is>
+      </c>
+      <c r="U20" t="inlineStr">
+        <is>
+          <t>Gävle</t>
+        </is>
+      </c>
+      <c r="V20" t="inlineStr">
+        <is>
+          <t>Gästrikland</t>
+        </is>
+      </c>
+      <c r="W20" t="inlineStr">
+        <is>
+          <t>Gävle</t>
+        </is>
+      </c>
+      <c r="Y20" t="inlineStr">
+        <is>
+          <t>2017-08-31</t>
+        </is>
+      </c>
+      <c r="AA20" t="inlineStr">
+        <is>
+          <t>2017-08-31</t>
+        </is>
+      </c>
+      <c r="AD20" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE20" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG20" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI20" t="inlineStr">
+        <is>
+          <t>olikåldrig gammal blandsumpskog</t>
+        </is>
+      </c>
+      <c r="AT20" t="inlineStr"/>
+      <c r="AW20" t="inlineStr">
+        <is>
+          <t>Magnus Andersson</t>
+        </is>
+      </c>
+      <c r="AX20" t="inlineStr">
+        <is>
+          <t>Magnus Andersson</t>
+        </is>
+      </c>
+      <c r="AY20" t="inlineStr"/>
+    </row>
+    <row r="21">
+      <c r="A21" t="n">
+        <v>73366627</v>
+      </c>
+      <c r="B21" t="n">
+        <v>103403</v>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>EN</t>
+        </is>
+      </c>
+      <c r="E21" t="n">
+        <v>223246</v>
+      </c>
+      <c r="F21" t="inlineStr">
+        <is>
+          <t>Skogsalm</t>
+        </is>
+      </c>
+      <c r="G21" t="inlineStr">
+        <is>
+          <t>Ulmus glabra</t>
+        </is>
+      </c>
+      <c r="H21" t="inlineStr">
+        <is>
+          <t>Huds.</t>
+        </is>
+      </c>
+      <c r="I21" t="inlineStr"/>
+      <c r="J21" t="inlineStr"/>
+      <c r="K21" t="inlineStr"/>
+      <c r="L21" t="inlineStr"/>
+      <c r="N21" t="inlineStr"/>
+      <c r="P21" t="inlineStr">
+        <is>
+          <t>Älgsjömuren norr om, Gstr</t>
+        </is>
+      </c>
+      <c r="Q21" t="n">
+        <v>623239</v>
+      </c>
+      <c r="R21" t="n">
+        <v>6724098</v>
+      </c>
+      <c r="S21" t="n">
+        <v>10</v>
+      </c>
+      <c r="T21" t="inlineStr">
+        <is>
+          <t>Gävleborg</t>
+        </is>
+      </c>
+      <c r="U21" t="inlineStr">
+        <is>
+          <t>Gävle</t>
+        </is>
+      </c>
+      <c r="V21" t="inlineStr">
+        <is>
+          <t>Gästrikland</t>
+        </is>
+      </c>
+      <c r="W21" t="inlineStr">
+        <is>
+          <t>Gävle</t>
+        </is>
+      </c>
+      <c r="Y21" t="inlineStr">
+        <is>
+          <t>2018-09-22</t>
+        </is>
+      </c>
+      <c r="AA21" t="inlineStr">
+        <is>
+          <t>2018-09-22</t>
+        </is>
+      </c>
+      <c r="AC21" t="inlineStr">
+        <is>
+          <t>buskformiga</t>
+        </is>
+      </c>
+      <c r="AD21" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE21" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF21" t="inlineStr"/>
+      <c r="AG21" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI21" t="inlineStr">
+        <is>
+          <t>kalkrik barrskog</t>
+        </is>
+      </c>
+      <c r="AT21" t="inlineStr"/>
+      <c r="AW21" t="inlineStr">
+        <is>
+          <t>Peter Ståhl</t>
+        </is>
+      </c>
+      <c r="AX21" t="inlineStr">
+        <is>
+          <t>Peter Ståhl, Inga-Greta Andersson</t>
+        </is>
+      </c>
+      <c r="AY21" t="inlineStr"/>
+    </row>
+    <row r="22">
+      <c r="A22" t="n">
+        <v>68512102</v>
+      </c>
+      <c r="B22" t="n">
+        <v>99036</v>
+      </c>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E22" t="n">
+        <v>223591</v>
+      </c>
+      <c r="F22" t="inlineStr">
+        <is>
+          <t>Skogsnycklar</t>
+        </is>
+      </c>
+      <c r="G22" t="inlineStr">
+        <is>
+          <t>Dactylorhiza maculata subsp. fuchsii</t>
+        </is>
+      </c>
+      <c r="H22" t="inlineStr">
+        <is>
+          <t>(Druce) Hyl.</t>
+        </is>
+      </c>
+      <c r="I22" t="inlineStr"/>
+      <c r="P22" t="inlineStr">
+        <is>
+          <t>Öster Älgsjön, Gstr</t>
+        </is>
+      </c>
+      <c r="Q22" t="n">
+        <v>623220</v>
+      </c>
+      <c r="R22" t="n">
+        <v>6723982</v>
+      </c>
+      <c r="S22" t="n">
+        <v>25</v>
+      </c>
+      <c r="T22" t="inlineStr">
+        <is>
+          <t>Gävleborg</t>
+        </is>
+      </c>
+      <c r="U22" t="inlineStr">
+        <is>
+          <t>Gävle</t>
+        </is>
+      </c>
+      <c r="V22" t="inlineStr">
+        <is>
+          <t>Gästrikland</t>
+        </is>
+      </c>
+      <c r="W22" t="inlineStr">
+        <is>
+          <t>Gävle</t>
+        </is>
+      </c>
+      <c r="Y22" t="inlineStr">
+        <is>
+          <t>2017-08-31</t>
+        </is>
+      </c>
+      <c r="AA22" t="inlineStr">
+        <is>
+          <t>2017-08-31</t>
+        </is>
+      </c>
+      <c r="AD22" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE22" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG22" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI22" t="inlineStr">
+        <is>
+          <t>olikåldrig gammal blandsumpskog</t>
+        </is>
+      </c>
+      <c r="AT22" t="inlineStr"/>
+      <c r="AW22" t="inlineStr">
+        <is>
+          <t>Magnus Andersson</t>
+        </is>
+      </c>
+      <c r="AX22" t="inlineStr">
+        <is>
+          <t>Magnus Andersson</t>
+        </is>
+      </c>
+      <c r="AY22" t="inlineStr"/>
+    </row>
+    <row r="23">
+      <c r="A23" t="n">
+        <v>73366614</v>
+      </c>
+      <c r="B23" t="n">
+        <v>106231</v>
+      </c>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E23" t="n">
+        <v>224098</v>
+      </c>
+      <c r="F23" t="inlineStr">
+        <is>
+          <t>Kalktallört</t>
+        </is>
+      </c>
+      <c r="G23" t="inlineStr">
+        <is>
+          <t>Monotropa hypophegea</t>
+        </is>
+      </c>
+      <c r="H23" t="inlineStr">
+        <is>
+          <t>Wallr.</t>
+        </is>
+      </c>
+      <c r="I23" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J23" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K23" t="inlineStr"/>
+      <c r="L23" t="inlineStr"/>
+      <c r="N23" t="inlineStr"/>
+      <c r="P23" t="inlineStr">
+        <is>
+          <t>Älgsjömuren norr om, Gstr</t>
+        </is>
+      </c>
+      <c r="Q23" t="n">
+        <v>623254</v>
+      </c>
+      <c r="R23" t="n">
+        <v>6724106</v>
+      </c>
+      <c r="S23" t="n">
+        <v>10</v>
+      </c>
+      <c r="T23" t="inlineStr">
+        <is>
+          <t>Gävleborg</t>
+        </is>
+      </c>
+      <c r="U23" t="inlineStr">
+        <is>
+          <t>Gävle</t>
+        </is>
+      </c>
+      <c r="V23" t="inlineStr">
+        <is>
+          <t>Gästrikland</t>
+        </is>
+      </c>
+      <c r="W23" t="inlineStr">
+        <is>
+          <t>Gävle</t>
+        </is>
+      </c>
+      <c r="Y23" t="inlineStr">
+        <is>
+          <t>2018-09-22</t>
+        </is>
+      </c>
+      <c r="AA23" t="inlineStr">
+        <is>
+          <t>2018-09-22</t>
+        </is>
+      </c>
+      <c r="AD23" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE23" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF23" t="inlineStr"/>
+      <c r="AG23" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI23" t="inlineStr">
+        <is>
+          <t>kalkrik barrskog</t>
+        </is>
+      </c>
+      <c r="AT23" t="inlineStr"/>
+      <c r="AW23" t="inlineStr">
+        <is>
+          <t>Peter Ståhl</t>
+        </is>
+      </c>
+      <c r="AX23" t="inlineStr">
+        <is>
+          <t>Peter Ståhl, Inga-Greta Andersson</t>
+        </is>
+      </c>
+      <c r="AY23" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 63702-2025 artfynd.xlsx
+++ b/artfynd/A 63702-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY23"/>
+  <dimension ref="A1:AZ23"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -789,6 +794,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/59966420</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -913,6 +923,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/73366562</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -1041,6 +1056,11 @@
           <t>Floraväkteri Sverige</t>
         </is>
       </c>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/74250550</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1152,6 +1172,11 @@
           <t>Gästriklands flora (2016)</t>
         </is>
       </c>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/91244189</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1277,6 +1302,11 @@
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/96852574</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -1402,6 +1432,11 @@
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127802330</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -1509,6 +1544,11 @@
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
+      <c r="AZ8" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/431483</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -1616,6 +1656,11 @@
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
+      <c r="AZ9" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/436422</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
@@ -1723,6 +1768,11 @@
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
+      <c r="AZ10" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/436423</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
@@ -1825,6 +1875,11 @@
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
+      <c r="AZ11" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/436685</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
@@ -1936,6 +1991,11 @@
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
+      <c r="AZ12" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/68512105</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
@@ -2045,6 +2105,11 @@
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
+      <c r="AZ13" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/96852676</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
@@ -2145,6 +2210,11 @@
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
+      <c r="AZ14" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/73366585</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
@@ -2256,6 +2326,11 @@
           <t>Gästriklands flora (2016)</t>
         </is>
       </c>
+      <c r="AZ15" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/93811407</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
@@ -2358,6 +2433,11 @@
         </is>
       </c>
       <c r="AY16" t="inlineStr"/>
+      <c r="AZ16" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/68512104</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="n">
@@ -2466,6 +2546,11 @@
         </is>
       </c>
       <c r="AY17" t="inlineStr"/>
+      <c r="AZ17" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/110157792</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="n">
@@ -2575,6 +2660,11 @@
         </is>
       </c>
       <c r="AY18" t="inlineStr"/>
+      <c r="AZ18" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/96853012</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="n">
@@ -2686,6 +2776,11 @@
           <t>Gästriklands flora (2016)</t>
         </is>
       </c>
+      <c r="AZ19" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/91244192</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="n">
@@ -2788,6 +2883,11 @@
         </is>
       </c>
       <c r="AY20" t="inlineStr"/>
+      <c r="AZ20" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/68512106</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="n">
@@ -2900,6 +3000,11 @@
         </is>
       </c>
       <c r="AY21" t="inlineStr"/>
+      <c r="AZ21" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/73366627</t>
+        </is>
+      </c>
     </row>
     <row r="22">
       <c r="A22" t="n">
@@ -3002,6 +3107,11 @@
         </is>
       </c>
       <c r="AY22" t="inlineStr"/>
+      <c r="AZ22" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/68512102</t>
+        </is>
+      </c>
     </row>
     <row r="23">
       <c r="A23" t="n">
@@ -3117,8 +3227,37 @@
         </is>
       </c>
       <c r="AY23" t="inlineStr"/>
+      <c r="AZ23" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/73366614</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ8" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ9" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ10" r:id="rId9"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ11" r:id="rId10"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ12" r:id="rId11"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ13" r:id="rId12"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ14" r:id="rId13"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ15" r:id="rId14"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ16" r:id="rId15"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ17" r:id="rId16"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ18" r:id="rId17"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ19" r:id="rId18"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ20" r:id="rId19"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ21" r:id="rId20"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ22" r:id="rId21"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ23" r:id="rId22"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>